--- a/Result/profitability/1475.xlsx
+++ b/Result/profitability/1475.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7325</v>
+        <v>0.60375</v>
       </c>
       <c r="N2" t="n">
-        <v>20.32125</v>
+        <v>18.9025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-2.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2887500000000001</v>
+        <v>0.06125000000000008</v>
       </c>
       <c r="N3" t="n">
-        <v>16.72125</v>
+        <v>15.8175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.4</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1362499999999999</v>
+        <v>-0.2449999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>13.78875</v>
+        <v>12.5925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.49</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.32875</v>
+        <v>-0.1612499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.23875</v>
+        <v>8.744999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2299999999999999</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>5.43375</v>
+        <v>4.88</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.55125</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>1.47</v>
+        <v>1.3975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.79875</v>
+        <v>-0.8862499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7874999999999999</v>
+        <v>-0.8362499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.74</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.59875</v>
+        <v>-0.5987499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-1.78875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>376</v>
+      </c>
+      <c r="D75" t="n">
+        <v>310</v>
+      </c>
+      <c r="E75" t="n">
+        <v>66</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.87375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.1875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7954545454545454</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.3900000000000006</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02179988820570156</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.155172413793103</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.949999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1841491841491841</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
